--- a/Content/Blueprints/Data/SpawnData/ExcelData/SpawnRawData.xlsx
+++ b/Content/Blueprints/Data/SpawnData/ExcelData/SpawnRawData.xlsx
@@ -9,11 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="7770" yWindow="2745" windowWidth="28800" windowHeight="15375"/>
+    <workbookView xWindow="7770" yWindow="2745" windowWidth="28800" windowHeight="15375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="스폰 raw 데이터" sheetId="1" r:id="rId1"/>
-    <sheet name="스탯 기초값" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="스탯 기초값" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'스폰 raw 데이터'!$A$1:$D$25</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>RowName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,6 +205,22 @@
   </si>
   <si>
     <t>speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">복붙용 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=VLOOKUP(D2,'[SpawnRawData.xlsx]스탯 기초값'!$A$2:$C$4,2,0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=VLOOKUP(D2,'[SpawnRawData.xlsx]스탯 기초값'!$A$2:$C$4,3,0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=QUOTIENT(B2/3,1)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -253,7 +270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -267,6 +284,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1286,13 +1306,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="61.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1302,8 +1334,11 @@
       <c r="C1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1313,8 +1348,17 @@
       <c r="C2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -1325,7 +1369,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>43</v>
       </c>
